--- a/data/trans_orig/IP42B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP42B-Habitat-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>665</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7125</t>
+          <t>7112</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22134</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35461</t>
+          <t>35287</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>59569</t>
+          <t>59582</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65948</t>
+          <t>66029</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,82 +1090,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>18,7%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5482</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>13,08%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>5984</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>2664</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>10238</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>7,17%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>3,19%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>18,8%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2055</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>681</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5484</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>13,09%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>5984</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>2693</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>10547</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>7,17%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33775</t>
+          <t>33814</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40266</t>
+          <t>39677</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,82 +1203,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>95,39%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>39849</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>36422</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>41222</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>95,1%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>86,92%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>77513</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>73259</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>80833</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>92,83%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>87,74%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>96,81%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>39849</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>36420</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>41223</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,1%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>86,91%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>77513</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>72950</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>80804</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>92,83%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>87,37%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6977</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,49 +1433,49 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>23,48%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2806</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>724</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6264</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>10,75%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
           <t>23,99%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2806</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6350</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>2,77%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>24,32%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>9</t>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10862</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22109</t>
+          <t>22258</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27757</t>
+          <t>27771</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,44 +1546,44 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>76,52%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,48%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>23306</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>19848</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>25388</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>89,25%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
           <t>76,01%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,43%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>23306</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>19762</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>25388</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>89,25%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>75,68%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
           <t>97,23%</t>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44335</t>
+          <t>44404</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52035</t>
+          <t>52385</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1553</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9898</t>
+          <t>9618</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5458</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15046</t>
+          <t>14938</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30371</t>
+          <t>30947</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37340</t>
+          <t>37388</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42653</t>
+          <t>42933</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49867</t>
+          <t>49910</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76397</t>
+          <t>76505</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>85985</t>
+          <t>86343</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,42%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7944</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18744</t>
+          <t>18363</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6922</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17956</t>
+          <t>17396</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16854</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32322</t>
+          <t>33111</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>117293</t>
+          <t>117674</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128435</t>
+          <t>128093</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>142839</t>
+          <t>143399</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>153873</t>
+          <t>153950</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>264510</t>
+          <t>263721</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>279978</t>
+          <t>279503</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,16%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1543</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>8653</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8371</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4739</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14455</t>
+          <t>14404</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28318</t>
+          <t>28055</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35165</t>
+          <t>34933</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34259</t>
+          <t>34459</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40682</t>
+          <t>41216</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>64882</t>
+          <t>64933</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74598</t>
+          <t>74620</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,05%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13638</t>
+          <t>13274</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11723</t>
+          <t>12421</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10390</t>
+          <t>10049</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22218</t>
+          <t>21590</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35023</t>
+          <t>35387</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43535</t>
+          <t>43834</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49253</t>
+          <t>48555</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>57590</t>
+          <t>57269</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>87419</t>
+          <t>88047</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>99247</t>
+          <t>99588</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,83%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14474</t>
+          <t>14898</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14134</t>
+          <t>14477</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13881</t>
+          <t>13466</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26721</t>
+          <t>25793</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>29,47%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32866</t>
+          <t>32442</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41316</t>
+          <t>41512</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26042</t>
+          <t>25699</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34811</t>
+          <t>34422</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60796</t>
+          <t>61724</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73636</t>
+          <t>74051</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,61%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2425</t>
+          <t>2267</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>10823</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10596</t>
+          <t>10475</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>7087</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18545</t>
+          <t>17353</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35495</t>
+          <t>35176</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43574</t>
+          <t>43732</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33656</t>
+          <t>33777</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>41551</t>
+          <t>41079</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>71706</t>
+          <t>72898</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>83238</t>
+          <t>83164</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,15%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20048</t>
+          <t>21221</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36695</t>
+          <t>37511</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19076</t>
+          <t>19449</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35275</t>
+          <t>35299</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44175</t>
+          <t>43786</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>66638</t>
+          <t>66645</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>142012</t>
+          <t>141196</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>158659</t>
+          <t>157486</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>152759</t>
+          <t>152735</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>168958</t>
+          <t>168585</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>300103</t>
+          <t>300096</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>322566</t>
+          <t>322955</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,06%</t>
         </is>
       </c>
     </row>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>694</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6517</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3597</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12671</t>
+          <t>12104</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5619</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16546</t>
+          <t>15071</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33925</t>
+          <t>33826</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39736</t>
+          <t>39649</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47529</t>
+          <t>48096</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56603</t>
+          <t>56705</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>83998</t>
+          <t>85473</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94925</t>
+          <t>95535</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>95,02%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2457</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9263</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9246</t>
+          <t>9538</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>6328</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15935</t>
+          <t>15827</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>58262</t>
+          <t>58330</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65068</t>
+          <t>65531</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>55756</t>
+          <t>55464</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>62558</t>
+          <t>62553</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>116592</t>
+          <t>116700</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>126502</t>
+          <t>126199</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,23%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>632</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5490</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11171</t>
+          <t>10689</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37017</t>
+          <t>37608</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43274</t>
+          <t>43220</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46054</t>
+          <t>45978</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50921</t>
+          <t>50912</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85412</t>
+          <t>85894</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>93482</t>
+          <t>93439</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2197</t>
+          <t>2180</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9317</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>1330</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7771</t>
+          <t>8076</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13744</t>
+          <t>14584</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39848</t>
+          <t>39595</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>46968</t>
+          <t>46985</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50019</t>
+          <t>49714</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>56543</t>
+          <t>56460</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93211</t>
+          <t>92371</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>102554</t>
+          <t>102042</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11426</t>
+          <t>12180</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24573</t>
+          <t>24540</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11986</t>
+          <t>11510</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24817</t>
+          <t>25294</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26344</t>
+          <t>26230</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45078</t>
+          <t>45458</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>177500</t>
+          <t>177533</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>190647</t>
+          <t>189893</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>209718</t>
+          <t>209241</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>222549</t>
+          <t>223025</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>391530</t>
+          <t>391150</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>410264</t>
+          <t>410378</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP42B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP42B-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -727,67 +727,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>1468</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5262</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,65%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,08%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>1392</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4285</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4327</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>5,26%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,19%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1468</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4942</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>754</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7112</t>
+          <t>6476</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>38761</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>34967</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>40229</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,35%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,92%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>25073</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>22180</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>22138</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>26465</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>94,74%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>83,81%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>83,65%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>38761</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>35287</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>40229</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,35%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>87,72%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>91</t>
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>59582</t>
+          <t>60218</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66029</t>
+          <t>65940</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>40229</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>40229</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>40229</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>26465</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>26465</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>26465</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>40229</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>40229</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>40229</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2055</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>681</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5439</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,98%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3929</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1916</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7779</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1324</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7284</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>9,45%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>18,7%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2055</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5482</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2664</t>
+          <t>2678</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10238</t>
+          <t>10719</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>39849</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>36465</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>41223</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,1%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,02%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>37664</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>33814</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>39677</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>34309</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>40269</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>90,55%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>81,3%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,39%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>39849</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>36422</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>41222</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,1%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>73259</t>
+          <t>72778</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>80833</t>
+          <t>80819</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41904</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41904</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41904</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>41593</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>41593</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>41593</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>41904</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>41904</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>41904</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2806</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>725</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6324</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,75%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>24,22%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3288</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1315</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6828</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6588</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>11,3%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>23,48%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2806</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>724</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>6264</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>23306</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>19788</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>25387</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,25%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>75,78%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,22%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>25798</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>22258</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>27771</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>22498</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>27788</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>88,7%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>76,52%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,48%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>23306</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>19848</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>25388</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>89,25%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44404</t>
+          <t>44837</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52385</t>
+          <t>52402</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,94%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>26112</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>26112</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>26112</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>29086</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>29086</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>29086</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>26112</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>26112</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>26112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5435</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2708</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10046</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>10,34%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19,12%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3888</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1505</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7946</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7826</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>10,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20,43%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5435</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2641</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9618</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>10,34%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14938</t>
+          <t>15573</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>47116</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>42505</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>49843</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>89,66%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>80,88%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,85%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>35005</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>30947</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>37388</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>31067</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>37521</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>90,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>79,57%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,13%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>47116</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>42933</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>49910</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>89,66%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>76505</t>
+          <t>75870</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>86343</t>
+          <t>85986</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>52551</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>52551</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>52551</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>38893</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>38893</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>38893</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>52551</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>52551</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>52551</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11764</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7026</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>17578</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,32%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,37%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10,93%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>12496</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7944</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>18363</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>7509</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>18963</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>9,19%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>13,5%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>11764</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>6845</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>17396</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17329</t>
+          <t>17297</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33111</t>
+          <t>31965</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>149031</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>143217</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>153769</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92,68%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>89,07%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,63%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>123541</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>117674</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>128093</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>117074</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>128528</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>90,81%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>86,5%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,16%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>149031</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>143399</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>153950</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>92,68%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>263721</t>
+          <t>264867</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>279503</t>
+          <t>279535</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,17%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>160795</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>160795</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>160795</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>136037</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>136037</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>136037</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>160795</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>160795</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>160795</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2501,7 +2501,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2674,67 +2674,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>4171</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1558</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>8388</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>9,79%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,66%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>19,68%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>4366</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1775</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8653</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1499</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8683</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>11,89%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>23,57%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4171</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>1414</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8171</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>9,79%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4717</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>13770</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,36%</t>
         </is>
       </c>
     </row>
@@ -2782,72 +2782,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>38459</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>34242</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>41072</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>90,21%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>80,32%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,34%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>32342</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>28055</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>34933</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>28025</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>35209</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>88,11%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>76,43%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,16%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>38459</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>34459</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>41216</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>90,21%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>64933</t>
+          <t>65567</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74620</t>
+          <t>74447</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,84%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>42630</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42630</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>42630</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>36708</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>36708</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>36708</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>42630</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>42630</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>42630</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6923</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3487</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11750</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>11,35%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,72%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19,27%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>8371</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4827</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>13274</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4937</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>13136</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>17,2%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,92%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>27,28%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>6923</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>3707</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>12421</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>11,35%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10049</t>
+          <t>10493</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21590</t>
+          <t>22002</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>54053</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>49226</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>57489</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>88,65%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>80,73%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,28%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>40290</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>35387</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>43834</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>35525</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>43724</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>82,8%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>72,72%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>90,08%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>54053</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>48555</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>57269</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>88,65%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>88047</t>
+          <t>87635</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>99588</t>
+          <t>99144</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,43%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>60976</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>60976</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>60976</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>48661</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>48661</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>48661</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>60976</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>60976</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>60976</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3355,72 +3355,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9340</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5478</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13845</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>23,25%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>13,63%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>34,46%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>9843</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5828</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14898</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6284</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>15418</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>20,79%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>31,47%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9340</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5754</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>14477</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>23,25%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13466</t>
+          <t>13426</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25793</t>
+          <t>26192</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>30836</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>26331</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>34698</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>76,75%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>65,54%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>86,37%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>37497</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>32442</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>41512</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>31922</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>41056</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>79,21%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>68,53%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>87,69%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>30836</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>25699</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>34422</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>76,75%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61724</t>
+          <t>61325</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>74051</t>
+          <t>74091</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,66%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>40176</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>40176</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>40176</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>47340</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>47340</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>47340</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>40176</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>40176</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>40176</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3698,72 +3698,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5959</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10344</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,47%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23,38%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>5644</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2267</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10823</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2468</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>10877</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>12,27%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>23,53%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>5959</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>3173</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>10475</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>13,47%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7087</t>
+          <t>6955</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17353</t>
+          <t>17932</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -3811,72 +3811,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>38293</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>33908</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>41021</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>86,53%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>76,62%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,7%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>40355</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>35176</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>43732</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>35122</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>43531</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>87,73%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>76,47%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,07%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>38293</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>33777</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>41079</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>86,53%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>72898</t>
+          <t>72319</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>83164</t>
+          <t>83296</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,29%</t>
         </is>
       </c>
     </row>
@@ -3929,52 +3929,52 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>44252</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>44252</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>44252</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>45999</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>45999</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>45999</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>44252</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>44252</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>44252</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4041,72 +4041,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>26394</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>18970</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>35036</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>14,04%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10,09%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>18,63%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>28224</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>21221</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>37511</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>20630</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>36151</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>15,79%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11,87%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>20,99%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>26394</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>19449</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>35299</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>14,04%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43786</t>
+          <t>43936</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>66645</t>
+          <t>65513</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -4154,72 +4154,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>161640</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>152998</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>169064</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>85,96%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>81,37%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>89,91%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>150483</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>141196</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>157486</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>142556</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>158077</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>84,21%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>79,01%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>88,13%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>161640</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>152735</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>168585</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>85,96%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>300096</t>
+          <t>301228</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>322955</t>
+          <t>322805</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>88,02%</t>
         </is>
       </c>
     </row>
@@ -4267,57 +4267,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>188034</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>188034</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>188034</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>178707</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>178707</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>178707</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>188034</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>188034</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>188034</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4448,7 +4448,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4616,72 +4616,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6809</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3577</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11892</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,31%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>19,75%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2732</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6517</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>782</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6575</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>6,77%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>16,15%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6809</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3495</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>12104</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>11,31%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>5395</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15071</t>
+          <t>15958</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>53391</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>48308</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>56623</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,69%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>80,25%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,06%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>37611</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>33826</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>39649</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>33768</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>39561</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>93,23%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>83,85%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,28%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>53391</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>48096</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>56705</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>88,69%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85473</t>
+          <t>84586</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>95535</t>
+          <t>95149</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,63%</t>
         </is>
       </c>
     </row>
@@ -4842,57 +4842,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60200</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60200</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60200</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>40343</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>40343</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>40343</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60200</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60200</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60200</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4964,67 +4964,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>5112</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2471</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9366</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>14,41%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>5101</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9195</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2393</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9498</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>7,55%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13,62%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5112</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9538</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,86%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6328</t>
+          <t>5778</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15827</t>
+          <t>15817</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>59890</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>55636</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>62531</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,14%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>85,59%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,2%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>62424</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>58330</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>65531</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>58027</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>65132</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>92,45%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>86,38%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,05%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>59890</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>55464</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>62553</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,14%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>116700</t>
+          <t>116710</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>126199</t>
+          <t>126749</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -5185,57 +5185,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>65002</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>65002</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>65002</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>67525</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>67525</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>67525</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>65002</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>65002</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>65002</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5302,72 +5302,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5319</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,9%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,32%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4173</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1819</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>7431</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1910</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8043</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>9,26%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,5%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5566</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10689</t>
+          <t>10594</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,12 +5397,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>49531</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>46225</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>50921</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,1%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>89,68%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,79%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>40866</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>37608</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>43220</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>36996</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>43129</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>90,74%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>83,5%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,96%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>49531</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>45978</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>50912</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,1%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>85894</t>
+          <t>85989</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>93439</t>
+          <t>93548</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,86%</t>
         </is>
       </c>
     </row>
@@ -5528,57 +5528,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>51544</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>51544</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>51544</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>45039</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>45039</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>45039</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>51544</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>51544</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>51544</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3634</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1179</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7826</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,29%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>13,54%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>5024</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2180</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>9570</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2162</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9734</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>10,22%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>19,47%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3634</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1330</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8076</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,29%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14584</t>
+          <t>14821</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -5758,72 +5758,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>54156</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>49964</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>56611</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,71%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>86,46%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,96%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>44141</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>39595</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>46985</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>39431</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>47003</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>89,78%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>80,53%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,57%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>54156</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>49714</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>56460</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,71%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>92371</t>
+          <t>92134</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>102042</t>
+          <t>102040</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -5871,57 +5871,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>57790</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>57790</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>57790</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>49165</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>49165</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>49165</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>57790</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>57790</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>57790</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>17567</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11284</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>24965</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,49%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10,64%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>17029</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>12180</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>24540</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>11500</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>24287</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>8,43%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,14%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>17567</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>11510</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>25294</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>7,49%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26230</t>
+          <t>26016</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45458</t>
+          <t>43951</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -6101,72 +6101,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>216968</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>209570</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>223251</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92,51%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>89,36%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,19%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>282</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>185044</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>177533</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>189893</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>177786</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>190573</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>91,57%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,86%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>93,97%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>216968</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>209241</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>223025</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>92,51%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>391150</t>
+          <t>392657</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>410378</t>
+          <t>410592</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -6214,57 +6214,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>234535</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>234535</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>234535</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>308</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>202073</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>202073</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>202073</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>234535</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>234535</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>234535</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
